--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/weekly/주차별 계획 W08.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/weekly/주차별 계획 W08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D196"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>주차</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>납기</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -441,11 +441,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>287</v>
+        <v>559</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>710</v>
+        <v>451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>473</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>930</v>
+        <v>754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -489,17 +489,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>278</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>683</v>
+        <v>384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -507,17 +507,17 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>961</v>
+        <v>62</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>435</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>209</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -543,17 +543,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>611</v>
+        <v>305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -561,17 +561,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>850</v>
+        <v>526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -579,17 +579,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>203</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256</v>
+        <v>706</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -615,17 +615,17 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>290</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>703</v>
+        <v>141</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -633,17 +633,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>459</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,17 +651,17 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>153</v>
+        <v>581</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -669,17 +669,17 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>404</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>751</v>
+        <v>783</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -687,17 +687,17 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>773</v>
+        <v>626</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -705,17 +705,17 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>498</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64</v>
+        <v>522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -723,17 +723,17 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -741,17 +741,17 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>429</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -759,17 +759,17 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>309</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>987</v>
+        <v>541</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -777,17 +777,17 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>304</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>802</v>
+        <v>630</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -795,17 +795,17 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>167</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>659</v>
+        <v>153</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>512</v>
+        <v>336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -831,17 +831,17 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>576</v>
+        <v>641</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -849,17 +849,17 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>481</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>452</v>
+        <v>617</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -867,17 +867,17 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>609</v>
+        <v>858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -885,17 +885,17 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>338</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>97</v>
+        <v>511</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>395</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -921,17 +921,17 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>408</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>740</v>
+        <v>387</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -939,17 +939,17 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>284</v>
+        <v>122</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -957,17 +957,17 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>738</v>
+        <v>325</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -975,17 +975,17 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167</v>
+        <v>903</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -993,17 +993,17 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>378</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>334</v>
+        <v>37</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1011,17 +1011,17 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>184</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>103</v>
+        <v>281</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1029,17 +1029,17 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>495</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>465</v>
+        <v>811</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1047,17 +1047,17 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>184</v>
+        <v>497</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>114</v>
+        <v>601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1065,17 +1065,17 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>201</v>
+        <v>62</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>220</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>580</v>
+        <v>184</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1101,17 +1101,17 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>284</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>427</v>
+        <v>748</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1119,17 +1119,17 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>52</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1137,17 +1137,17 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>181</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>305</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>813</v>
+        <v>980</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1173,17 +1173,17 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>166</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1191,17 +1191,17 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1209,17 +1209,17 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>398</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>752</v>
+        <v>432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1227,17 +1227,17 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>461</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>936</v>
+        <v>430</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1245,17 +1245,17 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>500</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>595</v>
+        <v>952</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1263,17 +1263,17 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>266</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>711</v>
+        <v>754</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>194</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>137</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>284</v>
+        <v>584</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1317,17 +1317,17 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>252</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>74</v>
+        <v>499</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>85</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1353,17 +1353,17 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>215</v>
+        <v>489</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1371,17 +1371,17 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>400</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1389,17 +1389,17 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>128</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>748</v>
+        <v>702</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1407,17 +1407,17 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>320</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>618</v>
+        <v>707</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1425,17 +1425,17 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>315</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>478</v>
+        <v>280</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1443,17 +1443,17 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>54</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>321</v>
+        <v>206</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>490</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1479,17 +1479,17 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>430</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>399</v>
+        <v>240</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1497,17 +1497,17 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>460</v>
+        <v>799</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>845</v>
+        <v>222</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1533,17 +1533,17 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>421</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>618</v>
+        <v>510</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1551,17 +1551,17 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>69</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>308</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1587,17 +1587,17 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>245</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>191</v>
+        <v>597</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1605,17 +1605,17 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>493</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1623,17 +1623,17 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>149</v>
+        <v>458</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>721</v>
+        <v>848</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1641,17 +1641,17 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>324</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1000</v>
+        <v>307</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1659,17 +1659,17 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>343</v>
+        <v>988</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1677,17 +1677,17 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>192</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>846</v>
+        <v>364</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1695,17 +1695,17 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>402</v>
+        <v>473</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>383</v>
+        <v>681</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>214</v>
+        <v>500</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1731,17 +1731,17 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>303</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>194</v>
+        <v>857</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1749,17 +1749,17 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>37</v>
+        <v>965</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>487</v>
+        <v>287</v>
       </c>
     </row>
     <row r="76">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1785,17 +1785,17 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>482</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>224</v>
+        <v>640</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1803,17 +1803,17 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>224</v>
+        <v>379</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>861</v>
+        <v>255</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>354</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>848</v>
+        <v>695</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1839,17 +1839,17 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>434</v>
+        <v>463</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>699</v>
+        <v>241</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1857,17 +1857,17 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>658</v>
+        <v>63</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1875,17 +1875,17 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>155</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>268</v>
+        <v>348</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1893,17 +1893,17 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>337</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>742</v>
+        <v>112</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1911,17 +1911,17 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>216</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1929,17 +1929,17 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>229</v>
+        <v>493</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>500</v>
+        <v>961</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>298</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>557</v>
+        <v>678</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>259</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1983,17 +1983,17 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>278</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>819</v>
+        <v>784</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2001,17 +2001,17 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>728</v>
+        <v>338</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2019,17 +2019,17 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>458</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>618</v>
+        <v>70</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>326</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>121</v>
+        <v>677</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>393</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>683</v>
+        <v>557</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2073,17 +2073,17 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>340</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>180</v>
+        <v>880</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2091,17 +2091,17 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>331</v>
+        <v>479</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>55</v>
+        <v>945</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2109,17 +2109,17 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>288</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>703</v>
+        <v>437</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2127,17 +2127,17 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>331</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1000</v>
+        <v>966</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2145,17 +2145,17 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>385</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>998</v>
+        <v>866</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2163,17 +2163,17 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>407</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>479</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>274</v>
+        <v>995</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2199,17 +2199,17 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>113</v>
+        <v>446</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>774</v>
+        <v>907</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2217,17 +2217,17 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>265</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>604</v>
+        <v>315</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>352</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>228</v>
+        <v>475</v>
       </c>
     </row>
     <row r="103">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>410</v>
+        <v>301</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2289,17 +2289,17 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>353</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>164</v>
+        <v>920</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2307,17 +2307,17 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>176</v>
+        <v>480</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>504</v>
+        <v>881</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2325,17 +2325,17 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>53</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>471</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>128</v>
+        <v>348</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>425</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>155</v>
+        <v>479</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>178</v>
+        <v>331</v>
       </c>
     </row>
     <row r="110">
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>361</v>
+        <v>745</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>233</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>543</v>
+        <v>764</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2415,17 +2415,17 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>247</v>
+        <v>172</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>497</v>
+        <v>591</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2433,17 +2433,17 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>49</v>
+        <v>345</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>749</v>
+        <v>189</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2451,17 +2451,17 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>356</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>336</v>
+        <v>928</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2469,17 +2469,17 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>34</v>
+        <v>207</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>55</v>
+        <v>537</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2487,17 +2487,17 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>414</v>
+        <v>167</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>127</v>
+        <v>420</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2505,17 +2505,17 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
+        <v>342</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>673</v>
+        <v>199</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2523,17 +2523,17 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>829</v>
+        <v>341</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>84</v>
+        <v>479</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2559,17 +2559,17 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>264</v>
+        <v>133</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>575</v>
+        <v>251</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2577,17 +2577,17 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>81</v>
+        <v>228</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>583</v>
+        <v>986</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2595,17 +2595,17 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>218</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>247</v>
+        <v>606</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2613,17 +2613,17 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>408</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2631,17 +2631,17 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>665</v>
+        <v>378</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2649,17 +2649,17 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>336</v>
+        <v>354</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>415</v>
+        <v>73</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2667,17 +2667,17 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>14</v>
+        <v>341</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>638</v>
+        <v>486</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2685,17 +2685,17 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>452</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2703,17 +2703,17 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>303</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>408</v>
+        <v>955</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>458</v>
       </c>
     </row>
     <row r="129">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>229</v>
+        <v>798</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>780</v>
+        <v>130</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2757,17 +2757,17 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>360</v>
+        <v>327</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>601</v>
+        <v>386</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2775,17 +2775,17 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>52</v>
+        <v>314</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2793,17 +2793,17 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>187</v>
+        <v>490</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>211</v>
+        <v>499</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2811,17 +2811,17 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>234</v>
+        <v>78</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>278</v>
+        <v>775</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2829,17 +2829,17 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>343</v>
+        <v>310</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>550</v>
+        <v>435</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2847,17 +2847,17 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>494</v>
+        <v>359</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>330</v>
+        <v>944</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2865,17 +2865,17 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>305</v>
+        <v>241</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>635</v>
+        <v>831</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2883,35 +2883,35 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B138" t="n">
+        <v>790</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
         <v>126</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>178</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>875</v>
+        <v>782</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2919,17 +2919,17 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>234</v>
+        <v>305</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>186</v>
+        <v>548</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2937,17 +2937,17 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>416</v>
+        <v>228</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2955,17 +2955,17 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>409</v>
+        <v>185</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2973,17 +2973,17 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>314</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2991,17 +2991,17 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>344</v>
+        <v>424</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>330</v>
+        <v>934</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>60</v>
+        <v>258</v>
       </c>
     </row>
     <row r="145">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>322</v>
+        <v>596</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>59</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>392</v>
+        <v>178</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3045,17 +3045,17 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>355</v>
+        <v>167</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>533</v>
+        <v>462</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3063,17 +3063,17 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>198</v>
+        <v>59</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>620</v>
+        <v>220</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>70</v>
+        <v>367</v>
       </c>
     </row>
     <row r="149">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>402</v>
+        <v>510</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3099,17 +3099,17 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>216</v>
+        <v>46</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3117,17 +3117,17 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>325</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>720</v>
+        <v>474</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3135,17 +3135,17 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>470</v>
+        <v>67</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>963</v>
+        <v>435</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3153,17 +3153,17 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>88</v>
+        <v>233</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3171,17 +3171,17 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>250</v>
+        <v>286</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>153</v>
+        <v>698</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3189,17 +3189,17 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>95</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>872</v>
+        <v>750</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3207,17 +3207,17 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64</v>
+        <v>270</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3225,17 +3225,17 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>443</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>984</v>
+        <v>773</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3243,17 +3243,17 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>996</v>
+        <v>362</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3279,17 +3279,17 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>287</v>
+        <v>358</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>678</v>
+        <v>564</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3297,17 +3297,17 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>711</v>
+        <v>966</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3315,17 +3315,17 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>737</v>
+        <v>303</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3333,17 +3333,17 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>430</v>
+        <v>209</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>510</v>
+        <v>797</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3351,17 +3351,17 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>588</v>
+        <v>756</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3369,17 +3369,17 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>15</v>
+        <v>330</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>309</v>
+        <v>393</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3387,17 +3387,17 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>16</v>
+        <v>456</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>240</v>
+        <v>469</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3405,17 +3405,17 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>275</v>
+        <v>445</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>182</v>
+        <v>394</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>399</v>
+        <v>41</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>589</v>
+        <v>997</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3441,17 +3441,17 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>572</v>
+        <v>146</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3459,17 +3459,17 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>596</v>
+        <v>131</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3477,17 +3477,17 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>803</v>
+        <v>412</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3495,457 +3495,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>565</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>788</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>569</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>114</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>779</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>905</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>279</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>459</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>804</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>224</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>612</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>891</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>657</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>640</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>843</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>593</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>297</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>182</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>309</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>283</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>931</v>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>148</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>950</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>897</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>728</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>443</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
